--- a/nurse_forms/009_nursing_family_event_leave_of_absence_form--nurse_forms.xlsx
+++ b/nurse_forms/009_nursing_family_event_leave_of_absence_form--nurse_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'family_event',_'value':_'family_event'}</t>
+          <t>family_event</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Family Event', 'value': 'family_event'}</t>
+          <t>Family Event</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other_event',_'value':_'other_event'}</t>
+          <t>other_event</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other Event', 'value': 'other_event'}</t>
+          <t>Other Event</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'approved',_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Approved', 'value': 'approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'denied',_'value':_'denied'}</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Denied', 'value': 'denied'}</t>
+          <t>Denied</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Pending', 'value': 'pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'supervisor',_'value':_'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Supervisor', 'value': 'supervisor'}</t>
+          <t>Supervisor</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Manager', 'value': 'manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'director',_'value':_'director'}</t>
+          <t>director</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Director', 'value': 'director'}</t>
+          <t>Director</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'manager',_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Manager', 'value': 'manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_lead',_'value':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team Lead', 'value': 'team_lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'director',_'value':_'director'}</t>
+          <t>director</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Director', 'value': 'director'}</t>
+          <t>Director</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'administrator',_'value':_'administrator'}</t>
+          <t>administrator</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Administrator', 'value': 'administrator'}</t>
+          <t>Administrator</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pending',_'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pending', 'value': 'pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'approved',_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Approved', 'value': 'approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rejected',_'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rejected', 'value': 'rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'In Progress', 'value': 'in_progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
